--- a/results/Int All Data -0.3/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_4_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9228896401397959</v>
+        <v>0.9236171150096626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9228267564143197</v>
+        <v>0.9244074736050054</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9209001787335146</v>
+        <v>0.9272516146744024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.921373244016883</v>
+        <v>0.9262726049026309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.921373244016883</v>
+        <v>0.9300885690323165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9204571179705876</v>
+        <v>0.929519740818437</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9183718936337953</v>
+        <v>0.9307517228344102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9142972078907217</v>
+        <v>0.9224093881449444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9149289198300774</v>
+        <v>0.922439392665386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9129694629442375</v>
+        <v>0.9235770490931448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9126536069745598</v>
+        <v>0.9246518217954274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9091791913081037</v>
+        <v>0.9263268645743274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9030836022960106</v>
+        <v>0.9262639808488513</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9030836022960106</v>
+        <v>0.9262639808488513</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.908547479368748</v>
+        <v>0.9279390236277514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9072211717645604</v>
+        <v>0.9282863214601673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.90220035545475</v>
+        <v>0.9267699253372544</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8967679202447506</v>
+        <v>0.9273073116883956</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8961990920308712</v>
+        <v>0.9273073116883956</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8950928774658505</v>
+        <v>0.9262968600538859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8941767514195551</v>
+        <v>0.9274659583443829</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8928818856781058</v>
+        <v>0.9282877588024638</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8996063119449613</v>
+        <v>0.9240858682661413</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8988473952123566</v>
+        <v>0.9234541563267855</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8971080313656836</v>
+        <v>0.9234541563267855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9035523555524893</v>
+        <v>0.9246546964800206</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9062035334185677</v>
+        <v>0.9254121758703288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9076570458160044</v>
+        <v>0.9262968600538859</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9076570458160044</v>
+        <v>0.9260124459469463</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8945125505135983</v>
+        <v>0.9286350566348799</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8945125505135983</v>
+        <v>0.9283506425279402</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8948612856883109</v>
+        <v>0.9286350566348799</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8902820927991306</v>
+        <v>0.9300256853068403</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8894602923410497</v>
+        <v>0.9293625315047465</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8894602923410497</v>
+        <v>0.9336901894920216</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8894602923410497</v>
+        <v>0.9342590177059011</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8914197492268895</v>
+        <v>0.9348907296452568</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8812394130756467</v>
+        <v>0.9384609082422237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8882211236135935</v>
+        <v>0.9358082930338487</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8774148248921814</v>
+        <v>0.9360927071407884</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8774148248921814</v>
+        <v>0.9341032457345071</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8775091504803958</v>
+        <v>0.9110457599480257</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8848652886866069</v>
+        <v>0.9231111705212593</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8804533665071935</v>
+        <v>0.9246904503696485</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8815910229349524</v>
+        <v>0.9249434226138501</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8720210182564032</v>
+        <v>0.9249434226138501</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8647563309538131</v>
+        <v>0.9249748644765883</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8602414591324058</v>
+        <v>0.8994262848223122</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7831566120979664</v>
+        <v>0.9158193533828211</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7828407561282885</v>
+        <v>0.9376762990160673</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7828407561282885</v>
+        <v>0.936317112206845</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7837254403118459</v>
+        <v>0.9257652230719311</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7780042789680169</v>
+        <v>0.9220063932985352</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.77130267051012</v>
+        <v>0.9295883739130997</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7655229374677047</v>
+        <v>0.9314835097311667</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.756708974837167</v>
+        <v>0.9304430535762154</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7499144781333523</v>
+        <v>0.9300957557437994</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7360396332764865</v>
+        <v>0.929148187834766</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.737677484823462</v>
+        <v>0.9253893580613701</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6908163529307769</v>
+        <v>0.9253893580613701</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6966318398628201</v>
+        <v>0.9269357587047247</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6933446380304961</v>
+        <v>0.9224194495410207</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6859498712500638</v>
+        <v>0.9218191794644031</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6909164278881776</v>
+        <v>0.9218191794644031</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7086101115593224</v>
+        <v>0.9155635064540262</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7079783996199667</v>
+        <v>0.8946555660721101</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7133165092417517</v>
+        <v>0.8808522289945</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7238984028971072</v>
+        <v>0.8594712233292153</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7191233721200152</v>
+        <v>0.8551135608214986</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7238984028971072</v>
+        <v>0.8487964414279421</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7168566833182772</v>
+        <v>0.854134551049727</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7182773165106791</v>
+        <v>0.8550821189587605</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7233338867101176</v>
+        <v>0.8405213024908423</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7236183008170572</v>
+        <v>0.8405213024908423</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7149644221848035</v>
+        <v>0.8416260797135664</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7057674078322219</v>
+        <v>0.8323076099369222</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7040637978751769</v>
+        <v>0.8378986918029088</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7040637978751769</v>
+        <v>0.8506901399037125</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6980296552462635</v>
+        <v>0.849869776787928</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7231567342720616</v>
+        <v>0.8589338369780741</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7183860155218594</v>
+        <v>0.8581763575877659</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7083028796434241</v>
+        <v>0.8586808647338725</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7083028796434241</v>
+        <v>0.8681865483446488</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7092204430320161</v>
+        <v>0.8705547494460842</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6972750505405485</v>
+        <v>0.870396102790097</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6942780121843506</v>
+        <v>0.8602858370758133</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6942465703216125</v>
+        <v>0.8558952953630619</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6924114435444286</v>
+        <v>0.8530197124309267</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.693076034688819</v>
+        <v>0.8458193461961095</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6933604487957588</v>
+        <v>0.8467983559678811</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.680569000694955</v>
+        <v>0.7688230753806982</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.681199275292014</v>
+        <v>0.7648455899104321</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6426290931016913</v>
+        <v>0.7823921256639623</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6426290931016913</v>
+        <v>0.7832768098475196</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6579545756714006</v>
+        <v>0.7835554745852729</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6522648561903099</v>
+        <v>0.8059070456363366</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6514545544706016</v>
+        <v>0.8059070456363366</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6409326698561292</v>
+        <v>0.8031029704834572</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6275666441722597</v>
+        <v>0.8037346824228129</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6251941310439346</v>
+        <v>0.7906830753663247</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6272164716552506</v>
+        <v>0.7623074230824236</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6938622609250591</v>
+        <v>0.7609024209874973</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6870435090699892</v>
+        <v>0.7416037649744117</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6700386716944899</v>
+        <v>0.7375276418890415</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6605915597823001</v>
+        <v>0.6711391368903243</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6616005740745132</v>
+        <v>0.6705388668137068</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6722854173718628</v>
+        <v>0.6576072778389845</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.681702524763611</v>
+        <v>0.4999340619221435</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6626081510244297</v>
+        <v>0.5021436163675916</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6615976993899201</v>
+        <v>0.5080176749982213</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5729993812241414</v>
+        <v>0.5080176749982213</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5692691186288905</v>
+        <v>0.4934311660367514</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5692691186288905</v>
+        <v>0.495610715961758</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5689847045219507</v>
+        <v>0.5369993467279262</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5699622769514258</v>
+        <v>0.5412341164692837</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5463844732535752</v>
+        <v>0.5333334052004481</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5568362874310884</v>
+        <v>0.5315654741756303</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4595384550151388</v>
+        <v>0.5305235806783825</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4689627491183702</v>
+        <v>0.5327732010403483</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4804665181892074</v>
+        <v>0.5083879703073828</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4801720426861915</v>
+        <v>0.5008331195286667</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4782668454720483</v>
+        <v>0.4926837480425195</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4790886459301293</v>
+        <v>0.5064700166803574</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5137285952781868</v>
+        <v>0.5056167743595382</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.512562371672283</v>
+        <v>0.5033743407090553</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5219480372012933</v>
+        <v>0.5090626228478494</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5465677343963917</v>
+        <v>0.5090626228478494</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5454987110632955</v>
+        <v>0.5065043332276887</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.549407563438899</v>
+        <v>0.5039160390870864</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5344279413593089</v>
+        <v>0.5025897314828989</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5146903569423993</v>
+        <v>0.5028741455898386</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4820998780415061</v>
+        <v>0.5022109917877448</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5085620683930585</v>
+        <v>0.5022109917877448</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5147277278421108</v>
+        <v>0.501895135818067</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5127382664358295</v>
+        <v>0.501895135818067</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4856104069331643</v>
+        <v>0.5022109917877448</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4869138967283933</v>
+        <v>0.5015792798483891</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.506538470107233</v>
+        <v>0.5015792798483891</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5220398474404887</v>
+        <v>0.4989566691604556</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5194157994102584</v>
+        <v>0.4989566691604556</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.502968471178053</v>
+        <v>0.4997470277557984</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5036316249801467</v>
+        <v>0.5009475679090335</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5015778425060925</v>
+        <v>0.5016107217111273</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5023038800336626</v>
+        <v>0.5016107217111273</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.501073335359986</v>
+        <v>0.5002829767646432</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.501073335359986</v>
+        <v>0.5005359490088447</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5008203631157844</v>
+        <v>0.4999671207949653</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5011047772227241</v>
+        <v>0.5012634238787113</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5008203631157844</v>
+        <v>0.5006945956648319</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4998713578644543</v>
+        <v>0.5006945956648319</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5006617164597972</v>
+        <v>0.5006945956648319</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4993354088556096</v>
+        <v>0.5006317119393556</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4992725251301334</v>
+        <v>0.5006317119393556</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.500251534901905</v>
+        <v>0.5003158559696779</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.500251534901905</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
